--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACEE406-C8F7-45FA-8BAB-E49FFD3A7796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16890"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +27,6 @@
     <t>产品子代码</t>
   </si>
   <si>
-    <t>产品名称</t>
-  </si>
-  <si>
     <t>产品主代码</t>
   </si>
   <si>
@@ -83,12 +79,16 @@
   </si>
   <si>
     <t>更新人</t>
+  </si>
+  <si>
+    <t>产品全称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -410,27 +410,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.75" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="15" width="12.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.44140625" style="1" customWidth="1"/>
-    <col min="17" max="18" width="12.88671875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="23.77734375" style="1" customWidth="1"/>
-    <col min="20" max="21" width="8.77734375" style="1"/>
+    <col min="11" max="15" width="12.5" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5" style="1" customWidth="1"/>
+    <col min="17" max="18" width="12.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="1" customWidth="1"/>
+    <col min="20" max="21" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,61 +438,61 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz001.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -81,7 +81,7 @@
     <t>更新人</t>
   </si>
   <si>
-    <t>产品全称</t>
+    <t>子产品名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
